--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,15 @@
       <c r="J1" t="str">
         <v>Durum</v>
       </c>
+      <c r="K1" t="str">
+        <v>Oda İndirimi (TL)</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Telefon</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Not</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -463,6 +472,15 @@
       <c r="J2" t="str">
         <v>CONFIRMED</v>
       </c>
+      <c r="K2" t="str">
+        <v>2500</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v>Örnek not</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -495,17 +513,26 @@
       <c r="J3" t="str">
         <v>CONFIRMED</v>
       </c>
+      <c r="K3" t="str">
+        <v>0</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -584,17 +611,27 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>8) "Oda İndirimi" yalnız oda gelirinden düşer; temizlik ücretini etkilemez.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v xml:space="preserve">   "Telefon" ve "Not" isteğe bağlıdır.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>Durum değerleri: CONFIRMED, CHECKED_IN, CHECKED_OUT, CANCELLED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -423,7 +423,7 @@
         <v>OTA Komisyonu (TL)</v>
       </c>
       <c r="H1" t="str">
-        <v>Temizlik Ücreti (TL)</v>
+        <v>Misafirden Temizlik Ücreti (TL)</v>
       </c>
       <c r="I1" t="str">
         <v>Kişi Sayısı</v>
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -586,52 +586,57 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>4) Brüt tutar temizlik ücretini İÇERİR; ayrıca "Temizlik Ücreti" sütununa</v>
+        <v>4) "Misafirden Temizlik Ücreti": misafirden ALINAN temizlik ücretidir (gelir);</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">   yazdığınız kısım gelir olarak ayrı raporlanır.</v>
+        <v xml:space="preserve">   brüt tutarın içindedir ve ayrı raporlanır. Personele ödenen temizlik</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5) Gece sayısı tarihlerden hesaplanır, ayrı sütun gerekmez.</v>
+        <v xml:space="preserve">   MALİYETİ bu dosyada yoktur; temizlik görevinden gider olarak yazılır.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>6) Başlık satırı DOSYANIN İLK SATIRI olmalıdır; üstüne rapor başlığı eklemeyin.</v>
+        <v>5) Gece sayısı tarihlerden hesaplanır, ayrı sütun gerekmez.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>7) Sütun sırası önemsizdir, fazladan sütunlar yok sayılır.</v>
+        <v>6) Başlık satırı DOSYANIN İLK SATIRI olmalıdır; üstüne rapor başlığı eklemeyin.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>8) "Oda İndirimi" yalnız oda gelirinden düşer; temizlik ücretini etkilemez.</v>
+        <v>7) Sütun sırası önemsizdir, fazladan sütunlar yok sayılır.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">   "Telefon" ve "Not" isteğe bağlıdır.</v>
+        <v>8) "Oda İndirimi" yalnız oda gelirinden düşer; temizlik ücretini etkilemez.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v xml:space="preserve">   "Telefon" ve "Not" isteğe bağlıdır.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
         <v>Durum değerleri: CONFIRMED, CHECKED_IN, CHECKED_OUT, CANCELLED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Rezervasyonlar" sheetId="1" r:id="rId1"/>
     <sheet name="NASIL DOLDURULUR" sheetId="2" r:id="rId2"/>
+    <sheet name="GEÇERLİ DEĞERLER" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -532,11 +533,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>LEXBNB — REZERVASYON DEFTERİ ŞABLONU</v>
+        <v>LEXBNB — REZERVASYON DEFTERİ ŞABLONU · NASIL DOLDURULUR</v>
       </c>
     </row>
     <row r="2">
@@ -546,97 +547,216 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ZORUNLU SÜTUNLAR: Villa, Misafir Adı, Giriş Tarihi, Çıkış Tarihi, Brüt Tutar</v>
+        <v>ADIM 1 — İlk sayfadaki örnek satırları silin ya da üzerine yazın. Başlık satırına dokunmayın: DOSYANIN İLK SATIRI olmalı, üstüne başlık eklemeyin.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Diğer sütunlar isteğe bağlıdır; boş bırakabilir veya tamamen silebilirsiniz.</v>
+        <v>ADIM 2 — Her rezervasyon bir satırdır. ZORUNLU: Villa, Misafir Adı, Giriş Tarihi, Çıkış Tarihi, Brüt Tutar. Diğer sütunları boş bırakabilir ya da silebilirsiniz.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>ADIM 3 — "Villa": kendi mülk kodunuzu yazın. MULK_KODU_1 / MULK_KODU_2 yalnız yer tutucudur; değiştirmezseniz o satırlar kaydedilmez (bilerek: yanlış mülke kayıt girmesin).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1) "Villa" sütununa KENDİ mülk kodunuzu yazın.</v>
+        <v>ADIM 4 — "Kanal": GEÇERLİ DEĞERLER sayfasındaki kanal kodu ya da adı (büyük/küçük harf önemsiz: airbnb = AIRBNB). Boşsa doğrudan satış sayılır. Listede olmayan kanalın satırı kaydedilmez ve nedeni yazılır.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">   MULK_KODU_1 / MULK_KODU_2 yalnızca yer tutucudur; değiştirmezseniz</v>
+        <v>ADIM 5 — Tarih: 2026-07-15 ya da 15.07.2026. Tutar: 72500 ya da 72.500,50. Gece sayısı tarihlerden hesaplanır.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">   hiçbir satır kaydedilmez (bilerek böyle — yanlış mülke kayıt girmeyin).</v>
+        <v>ADIM 6 — "Brüt Tutar" misafirin ödediği toplamdır. "Misafirden Temizlik Ücreti" bunun İÇİNDEDİR ve ayrı gelir olarak raporlanır. Personele ödenen temizlik MALİYETİ bu dosyaya yazılmaz.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2) Tarihler: 2026-07-15 veya 15.07.2026 — ikisi de kabul edilir.</v>
+        <v>ADIM 7 — "OTA Komisyonu" gider olarak yazılır, ciroyu düşürmez. "Oda İndirimi" yalnız oda gelirinden düşer.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>3) Tutar: 72500 veya 72.500,50 — ikisi de kabul edilir.</v>
+        <v>ADIM 8 — "Durum": GEÇERLİ DEĞERLER sayfasındaki değerlerden biri; boşsa CONFIRMED.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>4) "Misafirden Temizlik Ücreti": misafirden ALINAN temizlik ücretidir (gelir);</v>
+        <v>ADIM 9 — Kaydedip Araçlar › Excel / CSV yükle ekranına bırakın. Önizlemede her hatalı satırı ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">   brüt tutarın içindedir ve ayrı raporlanır. Personele ödenen temizlik</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">   MALİYETİ bu dosyada yoktur; temizlik görevinden gider olarak yazılır.</v>
+        <v>Elinizde başka biçimde bir tablo mu var? Aynı ekrandaki "Tablomu şablona çevir (ChatGPT)" düğmesi, tablonuzu bu sütunlara çevirecek hazır bir istem kopyalar.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B21"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>MÜLKLER — "Villa" sütununa KODU ya da ADI yazın</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Kod</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Ad</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>MULK_KODU_1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>MULK_KODU_2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>KANALLAR — "Kanal" sütununa KODU ya da ADI yazın (sistem kanalları; kendi eklediğiniz kanallar uygulama içi şablonda görünür)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Kod</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ad</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>WHATSAPP</v>
+      </c>
+      <c r="B8" t="str">
+        <v>WhatsApp</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AIRBNB</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Airbnb</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BOOKING</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Booking.com</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>INSTAGRAM</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Instagram</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>WEBSITE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Website</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>REPEAT</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Tekrar Misafir</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5) Gece sayısı tarihlerden hesaplanır, ayrı sütun gerekmez.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>6) Başlık satırı DOSYANIN İLK SATIRI olmalıdır; üstüne rapor başlığı eklemeyin.</v>
+        <v>PHONE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Telefon</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>7) Sütun sırası önemsizdir, fazladan sütunlar yok sayılır.</v>
+        <v>DURUM — "Durum" sütunu</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>8) "Oda İndirimi" yalnız oda gelirinden düşer; temizlik ücretini etkilemez.</v>
+        <v>Değer</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Anlamı</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">   "Telefon" ve "Not" isteğe bağlıdır.</v>
+        <v>CONFIRMED</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Onaylı (henüz giriş yapmadı)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>CHECKED_IN</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Konaklıyor</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Durum değerleri: CONFIRMED, CHECKED_IN, CHECKED_OUT, CANCELLED</v>
+        <v>CHECKED_OUT</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Çıkış yaptı (tamamlandı)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CANCELLED</v>
+      </c>
+      <c r="B21" t="str">
+        <v>İptal (ciroya girmez)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -572,7 +572,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ADIM 6 — "Brüt Tutar" misafirin ödediği toplamdır. "Misafirden Temizlik Ücreti" bunun İÇİNDEDİR ve ayrı gelir olarak raporlanır. Personele ödenen temizlik MALİYETİ bu dosyaya yazılmaz.</v>
+        <v>ADIM 6 — "Brüt Tutar" misafirin ödediği toplamdır. "Misafirden Temizlik Ücreti" bunun İÇİNDEDİR ve ayrı gelir olarak raporlanır. Personele ödenen temizlik MALİYETİ bu dosyaya yazılmaz; geçmiş temizlik maliyetleri için Geçmiş Temizlik şablonunu kullanın.</v>
       </c>
     </row>
     <row r="9">

--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -587,7 +587,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ADIM 9 — Kaydedip Araçlar › Excel / CSV yükle ekranına bırakın. Önizlemede her hatalı satırı ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
+        <v>ADIM 9 — Kaydedip Veri ve yardım › Excel / CSV yükle ekranına bırakın. Önizlemede her hatalı satırı ve nedenini görürsünüz; onaylamadan hiçbir şey kaydedilmez.</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         <v>MULK_KODU_1</v>
       </c>
       <c r="B3" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +637,7 @@
         <v>MULK_KODU_2</v>
       </c>
       <c r="B4" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="6">

--- a/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
+++ b/sablonlar/lexbnb-rezervasyon-sablonu.xlsx
@@ -552,7 +552,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ADIM 2 — Her rezervasyon bir satırdır. ZORUNLU: Villa, Misafir Adı, Giriş Tarihi, Çıkış Tarihi, Brüt Tutar. Diğer sütunları boş bırakabilir ya da silebilirsiniz.</v>
+        <v>ADIM 2 — Her rezervasyon bir satırdır. ZORUNLU: Villa, Misafir Adı, Giriş Tarihi, Çıkış Tarihi, Brüt Tutar, Kişi Sayısı (kişi sayısı tahmin edilmez; boş satır kaydedilmez). Diğer sütunları boş bırakabilir ya da silebilirsiniz.</v>
       </c>
     </row>
     <row r="5">
